--- a/output/pdf_financials_xlsx/GLDR.xlsx
+++ b/output/pdf_financials_xlsx/GLDR.xlsx
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.119816</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.245844</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.232077</v>
       </c>
     </row>
     <row r="93">
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.0475</v>
+        <v>-0.129008</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.035</v>
+        <v>-0.119827</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.176508</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.5483980000000001</v>
       </c>
     </row>
     <row r="119">
@@ -3730,7 +3730,11 @@
           <t>Warrants reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3946,7 +3950,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4374,7 +4382,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.176508</v>
       </c>

--- a/output/pdf_financials_xlsx/GLDR.xlsx
+++ b/output/pdf_financials_xlsx/GLDR.xlsx
@@ -607,10 +607,10 @@
         <v>0.112502</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.458421</v>
+        <v>1.018708</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.424746</v>
+        <v>0.5709959999999999</v>
       </c>
     </row>
     <row r="11">
@@ -626,10 +626,10 @@
         <v>-0.112502</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.458421</v>
+        <v>-1.018708</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.424746</v>
+        <v>-0.5709959999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.150009</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.714298</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.544635</v>
       </c>
     </row>
     <row r="35">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.150009</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.714298</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.544635</v>
       </c>
     </row>
     <row r="37">
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.177509</v>
+        <v>0.0275</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.7247980000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.618385</v>
+        <v>0.07375</v>
       </c>
     </row>
     <row r="49">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-1.018708</v>
+        <v>1.018708</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>-0.5709959999999999</v>
+        <v>0.5709959999999999</v>
       </c>
     </row>
     <row r="68">

--- a/output/pdf_financials_xlsx/GLDR.xlsx
+++ b/output/pdf_financials_xlsx/GLDR.xlsx
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011751</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3123,13 +3123,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011751</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.625293</v>
+        <v>-0.628293</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.099413</v>
+        <v>-0.111164</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.625293</v>
+        <v>-0.628293</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.571115</v>
@@ -4350,7 +4350,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.003</v>
       </c>
@@ -4450,7 +4454,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.30024</v>
       </c>
